--- a/files/1-kontent-plan-na-mesyac.xlsx
+++ b/files/1-kontent-plan-na-mesyac.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Польза</t>
+          <t>AI-инструменты</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>5 шаблонов, которые экономят время</t>
+          <t>5 нейросетей, которые экономят часы в неделю</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Кейс</t>
+          <t>Автоматизация</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Сторис</t>
+          <t>Карусель</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Как сократила отчёт с 3 часов до 20 минут</t>
+          <t>Как я сократила отчёт с 3 часов до 20 минут</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Польза</t>
+          <t>AI-инструменты</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1224,41 +1224,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Подборки, чек-листы</t>
+          <t>Подборки, обзоры за 30 секунд</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Мышление</t>
+          <t>Автоматизация</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Доверие и удержание</t>
+          <t>Польза и сохранения</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Короткие мысли</t>
+          <t>Чек-листы, шаблоны, кейсы</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Кейс</t>
+          <t>Мышление</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Доверие и удержание</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Разбор своей работы</t>
+          <t>Короткие мысли, честные признания</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Оффер, отзывы</t>
+          <t>Оффер, отзывы, разбор услуги</t>
         </is>
       </c>
     </row>
